--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="131">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -244,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>Patient2.IntegrationControlNumber</t>
+    <t>Patient2.integrationControlNumber</t>
   </si>
   <si>
     <t>1</t>
@@ -254,159 +257,159 @@
 </t>
   </si>
   <si>
-    <t>INTEGRATION CONTROL NUMBER (991.01)</t>
-  </si>
-  <si>
-    <t>Patient2.Name</t>
-  </si>
-  <si>
-    <t>NAME (.01)</t>
-  </si>
-  <si>
-    <t>Patient2.PhoneNumberResidence</t>
-  </si>
-  <si>
-    <t>PHONE NUMBER [RESIDENCE] (.131)</t>
-  </si>
-  <si>
-    <t>Patient2.PhoneNumberWork</t>
-  </si>
-  <si>
-    <t>PHONE NUMBER [WORK] (.132)</t>
-  </si>
-  <si>
-    <t>Patient2.PhoneNumberCellular</t>
-  </si>
-  <si>
-    <t>PHONE NUMBER [CELLULAR] (.134)</t>
-  </si>
-  <si>
-    <t>Patient2.DateOfBirth</t>
-  </si>
-  <si>
-    <t>DATE OF BIRTH (.03)</t>
-  </si>
-  <si>
-    <t>Patient2.DateOfDeath</t>
-  </si>
-  <si>
-    <t>DATE OF DEATH (.351)</t>
-  </si>
-  <si>
-    <t>Patient2.StreetAddressLine1</t>
-  </si>
-  <si>
-    <t>STREET ADDRESS [LINE 1] (.111)</t>
-  </si>
-  <si>
-    <t>Patient2.StreetAddressLine2</t>
-  </si>
-  <si>
-    <t>STREET ADDRESS [LINE 2] (.112)</t>
-  </si>
-  <si>
-    <t>Patient2.StreetAddressLine3</t>
-  </si>
-  <si>
-    <t>STREET ADDRESS [LINE 3] (.113)</t>
-  </si>
-  <si>
-    <t>Patient2.City</t>
-  </si>
-  <si>
-    <t>CITY (.114)</t>
-  </si>
-  <si>
-    <t>Patient2.State</t>
-  </si>
-  <si>
-    <t>STATE (.115)</t>
-  </si>
-  <si>
-    <t>Patient2.Zip4</t>
-  </si>
-  <si>
-    <t>ZIP+4 (.1112)</t>
-  </si>
-  <si>
-    <t>Patient2.Country</t>
-  </si>
-  <si>
-    <t>COUNTRY (.1173)</t>
-  </si>
-  <si>
-    <t>Patient2.TemporaryAddressStartDate</t>
-  </si>
-  <si>
-    <t>TEMPORARY ADDRESS START DATE (.1217)</t>
-  </si>
-  <si>
-    <t>Patient2.TemporaryAddressEndDate</t>
-  </si>
-  <si>
-    <t>TEMPORARY ADDRESS END DATE (.1218)</t>
-  </si>
-  <si>
-    <t>Patient2.LanguageDatetime</t>
+    <t>INTEGRATION CONTROL NUMBER (-991.01)</t>
+  </si>
+  <si>
+    <t>Patient2.name</t>
+  </si>
+  <si>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>Patient2.phoneNumberResidence</t>
+  </si>
+  <si>
+    <t>PHONE NUMBER [RESIDENCE] (-.131)</t>
+  </si>
+  <si>
+    <t>Patient2.phoneNumberWork</t>
+  </si>
+  <si>
+    <t>PHONE NUMBER [WORK] (-.132)</t>
+  </si>
+  <si>
+    <t>Patient2.phoneNumberCellular</t>
+  </si>
+  <si>
+    <t>PHONE NUMBER [CELLULAR] (-.134)</t>
+  </si>
+  <si>
+    <t>Patient2.dateOfBirth</t>
+  </si>
+  <si>
+    <t>DATE OF BIRTH (-.03)</t>
+  </si>
+  <si>
+    <t>Patient2.dateOfDeath</t>
+  </si>
+  <si>
+    <t>DATE OF DEATH (-.351)</t>
+  </si>
+  <si>
+    <t>Patient2.streetAddressLine1</t>
+  </si>
+  <si>
+    <t>STREET ADDRESS [LINE 1] (-.111)</t>
+  </si>
+  <si>
+    <t>Patient2.streetAddressLine2</t>
+  </si>
+  <si>
+    <t>STREET ADDRESS [LINE 2] (-.112)</t>
+  </si>
+  <si>
+    <t>Patient2.streetAddressLine3</t>
+  </si>
+  <si>
+    <t>STREET ADDRESS [LINE 3] (-.113)</t>
+  </si>
+  <si>
+    <t>Patient2.city</t>
+  </si>
+  <si>
+    <t>CITY (-.114)</t>
+  </si>
+  <si>
+    <t>Patient2.state</t>
+  </si>
+  <si>
+    <t>STATE (-.115)</t>
+  </si>
+  <si>
+    <t>Patient2.zip4</t>
+  </si>
+  <si>
+    <t>ZIP+4 (-.1112)</t>
+  </si>
+  <si>
+    <t>Patient2.country</t>
+  </si>
+  <si>
+    <t>COUNTRY (-.1173)</t>
+  </si>
+  <si>
+    <t>Patient2.temporaryAddressStartDate</t>
+  </si>
+  <si>
+    <t>TEMPORARY ADDRESS START DATE (-.1217)</t>
+  </si>
+  <si>
+    <t>Patient2.temporaryAddressEndDate</t>
+  </si>
+  <si>
+    <t>TEMPORARY ADDRESS END DATE (-.1218)</t>
+  </si>
+  <si>
+    <t>Patient2.languageDatetime</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LanguageDatetime207)
 </t>
   </si>
   <si>
-    <t>LANGUAGE DATE/TIME (7)</t>
-  </si>
-  <si>
-    <t>Patient2.Sex</t>
-  </si>
-  <si>
-    <t>SEX (.02)</t>
-  </si>
-  <si>
-    <t>Patient2.SelfIdentifiedGender</t>
-  </si>
-  <si>
-    <t>SELF IDENTIFIED GENDER (.024)</t>
-  </si>
-  <si>
-    <t>Patient2.EthnicityInformation</t>
-  </si>
-  <si>
-    <t>ETHNICITY INFORMATION (6)</t>
-  </si>
-  <si>
-    <t>Patient2.RaceInformation</t>
-  </si>
-  <si>
-    <t>RACE INFORMATION (2)</t>
-  </si>
-  <si>
-    <t>Patient2.MaritalStatus</t>
-  </si>
-  <si>
-    <t>MARITAL STATUS (.05)</t>
-  </si>
-  <si>
-    <t>Patient2.ReligiousPreference</t>
-  </si>
-  <si>
-    <t>RELIGIOUS PREFERENCE (.08)</t>
-  </si>
-  <si>
-    <t>Patient2.Patient</t>
-  </si>
-  <si>
-    <t>PATIENT ()</t>
-  </si>
-  <si>
-    <t>Patient2.LaboratoryReference</t>
+    <t>LANGUAGE DATE/TIME (-7)</t>
+  </si>
+  <si>
+    <t>Patient2.sex</t>
+  </si>
+  <si>
+    <t>SEX (-.02)</t>
+  </si>
+  <si>
+    <t>Patient2.selfIdentifiedGender</t>
+  </si>
+  <si>
+    <t>SELF IDENTIFIED GENDER (-.024)</t>
+  </si>
+  <si>
+    <t>Patient2.ethnicityInformation</t>
+  </si>
+  <si>
+    <t>ETHNICITY INFORMATION (-6)</t>
+  </si>
+  <si>
+    <t>Patient2.raceInformation</t>
+  </si>
+  <si>
+    <t>RACE INFORMATION (-2)</t>
+  </si>
+  <si>
+    <t>Patient2.maritalStatus</t>
+  </si>
+  <si>
+    <t>MARITAL STATUS (-.05)</t>
+  </si>
+  <si>
+    <t>Patient2.religiousPreference</t>
+  </si>
+  <si>
+    <t>RELIGIOUS PREFERENCE (-.08)</t>
+  </si>
+  <si>
+    <t>Patient2.patient</t>
+  </si>
+  <si>
+    <t>PATIENT (-)</t>
+  </si>
+  <si>
+    <t>Patient2.laboratoryReference</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabData63)
 </t>
   </si>
   <si>
-    <t>LABORATORY REFERENCE (63)</t>
+    <t>LABORATORY REFERENCE (-63)</t>
   </si>
 </sst>
 </file>
@@ -637,39 +640,41 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -677,26 +682,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -709,8 +714,8 @@
   <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.52734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.52734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.12890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.12890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -740,7 +745,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.52734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.12890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -748,112 +753,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -865,2593 +870,2595 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="138">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -363,9 +363,19 @@
     <t>Patient2.sex</t>
   </si>
   <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
     <t>SEX (-.02)</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity-vista</t>
+  </si>
+  <si>
     <t>Patient2.selfIdentifiedGender</t>
   </si>
   <si>
@@ -378,22 +388,34 @@
     <t>ETHNICITY INFORMATION (-6)</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory-vista</t>
+  </si>
+  <si>
     <t>Patient2.raceInformation</t>
   </si>
   <si>
     <t>RACE INFORMATION (-2)</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFraceCategory-vista</t>
+  </si>
+  <si>
     <t>Patient2.maritalStatus</t>
   </si>
   <si>
     <t>MARITAL STATUS (-.05)</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus-vista</t>
+  </si>
+  <si>
     <t>Patient2.religiousPreference</t>
   </si>
   <si>
     <t>RELIGIOUS PREFERENCE (-.08)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
   </si>
   <si>
     <t>Patient2.patient</t>
@@ -739,7 +761,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.08984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -2689,13 +2711,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2722,13 +2744,11 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2763,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2789,13 +2809,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2822,13 +2842,11 @@
         <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>
@@ -2846,7 +2864,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -2863,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2889,13 +2907,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2922,13 +2940,11 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -2946,7 +2962,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -2963,10 +2979,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -2989,13 +3005,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3022,13 +3038,11 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3046,7 +3060,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3063,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3089,13 +3103,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3122,13 +3136,11 @@
         <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>72</v>
@@ -3146,7 +3158,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3163,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3189,13 +3201,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3222,13 +3234,11 @@
         <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>72</v>
@@ -3246,7 +3256,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3263,10 +3273,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3292,10 +3302,10 @@
         <v>79</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3346,7 +3356,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3363,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3389,13 +3399,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3446,7 +3456,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -373,15 +373,18 @@
     <t>example</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFbirthSex-vista</t>
+  </si>
+  <si>
+    <t>Patient2.selfIdentifiedGender</t>
+  </si>
+  <si>
+    <t>SELF IDENTIFIED GENDER (-.024)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity-vista</t>
   </si>
   <si>
-    <t>Patient2.selfIdentifiedGender</t>
-  </si>
-  <si>
-    <t>SELF IDENTIFIED GENDER (-.024)</t>
-  </si>
-  <si>
     <t>Patient2.ethnicityInformation</t>
   </si>
   <si>
@@ -418,10 +421,10 @@
     <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
   </si>
   <si>
-    <t>Patient2.patient</t>
-  </si>
-  <si>
-    <t>PATIENT (-)</t>
+    <t>Patient2.appointment</t>
+  </si>
+  <si>
+    <t>APPOINTMENT (-1900)</t>
   </si>
   <si>
     <t>Patient2.laboratoryReference</t>
@@ -2846,7 +2849,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>
@@ -2881,10 +2884,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2910,10 +2913,10 @@
         <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2944,7 +2947,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -2962,7 +2965,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -2979,10 +2982,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3008,10 +3011,10 @@
         <v>115</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3042,7 +3045,7 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3060,7 +3063,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3077,10 +3080,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3106,10 +3109,10 @@
         <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3140,7 +3143,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>72</v>
@@ -3158,7 +3161,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3175,10 +3178,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3204,10 +3207,10 @@
         <v>115</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3238,7 +3241,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>72</v>
@@ -3256,7 +3259,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3273,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3302,10 +3305,10 @@
         <v>79</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3356,7 +3359,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3373,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3399,13 +3402,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3456,7 +3459,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>-</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file PATIENT (2)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -370,7 +370,7 @@
     <t>SEX (-.02)</t>
   </si>
   <si>
-    <t>example</t>
+    <t>preferred</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFbirthSex-vista</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -373,7 +373,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFbirthSex-vista</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFadminGender-vista</t>
   </si>
   <si>
     <t>Patient2.selfIdentifiedGender</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,16 +247,32 @@
     <t>Base</t>
   </si>
   <si>
-    <t>Patient2.integrationControlNumber</t>
+    <t>Patient2.laboratoryReference</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabData63)
+</t>
+  </si>
+  <si>
+    <t>LABORATORY REFERENCE (-63)</t>
+  </si>
+  <si>
+    <t>Patient2.appointment</t>
   </si>
   <si>
     <t xml:space="preserve">Element
 </t>
   </si>
   <si>
+    <t>APPOINTMENT (-1900)</t>
+  </si>
+  <si>
+    <t>Patient2.integrationControlNumber</t>
+  </si>
+  <si>
     <t>INTEGRATION CONTROL NUMBER (-991.01)</t>
   </si>
   <si>
@@ -419,22 +435,6 @@
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
-  </si>
-  <si>
-    <t>Patient2.appointment</t>
-  </si>
-  <si>
-    <t>APPOINTMENT (-1900)</t>
-  </si>
-  <si>
-    <t>Patient2.laboratoryReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabData63)
-</t>
-  </si>
-  <si>
-    <t>LABORATORY REFERENCE (-63)</t>
   </si>
 </sst>
 </file>
@@ -1114,13 +1114,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1214,13 +1214,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1271,7 +1271,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1314,13 +1314,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1371,7 +1371,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1414,13 +1414,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1471,7 +1471,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1514,13 +1514,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1571,7 +1571,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1614,13 +1614,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1671,7 +1671,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1714,13 +1714,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1771,7 +1771,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1814,13 +1814,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1871,7 +1871,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1914,13 +1914,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1971,7 +1971,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2014,13 +2014,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2071,7 +2071,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2114,13 +2114,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2171,7 +2171,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2214,13 +2214,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2271,7 +2271,7 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2288,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2314,13 +2314,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2371,7 +2371,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2414,13 +2414,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2471,7 +2471,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2514,13 +2514,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2571,7 +2571,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2614,7 +2614,7 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>113</v>
@@ -2671,7 +2671,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2714,13 +2714,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2747,11 +2747,13 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2786,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2812,13 +2814,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2845,11 +2847,13 @@
         <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>
@@ -2867,7 +2871,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -2884,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2910,13 +2914,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2943,11 +2947,11 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -2965,7 +2969,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -2982,10 +2986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3008,13 +3012,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3041,11 +3045,11 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3063,7 +3067,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3080,10 +3084,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3106,13 +3110,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3139,11 +3143,11 @@
         <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>72</v>
@@ -3161,7 +3165,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3178,10 +3182,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3204,13 +3208,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3237,11 +3241,11 @@
         <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>72</v>
@@ -3259,7 +3263,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3276,10 +3280,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3302,13 +3306,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3335,13 +3339,11 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>72</v>
@@ -3359,7 +3361,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3402,13 +3404,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3435,13 +3437,11 @@
         <v>72</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>72</v>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file PATIENT (2)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source PATIENT (2)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,20 @@
     <t>Base</t>
   </si>
   <si>
+    <t>Patient2.appointment</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element
+</t>
+  </si>
+  <si>
+    <t>APPOINTMENT (-1900)</t>
+  </si>
+  <si>
     <t>Patient2.laboratoryReference</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabData63)
@@ -260,16 +270,6 @@
     <t>LABORATORY REFERENCE (-63)</t>
   </si>
   <si>
-    <t>Patient2.appointment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Element
-</t>
-  </si>
-  <si>
-    <t>APPOINTMENT (-1900)</t>
-  </si>
-  <si>
     <t>Patient2.integrationControlNumber</t>
   </si>
   <si>
@@ -392,6 +392,42 @@
     <t>http://va.gov/fhir/ValueSet/VSVFadminGender-vista</t>
   </si>
   <si>
+    <t>Patient2.ethnicityInformation</t>
+  </si>
+  <si>
+    <t>ETHNICITY INFORMATION (-6)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory-vista</t>
+  </si>
+  <si>
+    <t>Patient2.raceInformation</t>
+  </si>
+  <si>
+    <t>RACE INFORMATION (-2)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFraceCategory-vista</t>
+  </si>
+  <si>
+    <t>Patient2.maritalStatus</t>
+  </si>
+  <si>
+    <t>MARITAL STATUS (-.05)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus-vista</t>
+  </si>
+  <si>
+    <t>Patient2.religiousPreference</t>
+  </si>
+  <si>
+    <t>RELIGIOUS PREFERENCE (-.08)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
+  </si>
+  <si>
     <t>Patient2.selfIdentifiedGender</t>
   </si>
   <si>
@@ -399,42 +435,6 @@
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity-vista</t>
-  </si>
-  <si>
-    <t>Patient2.ethnicityInformation</t>
-  </si>
-  <si>
-    <t>ETHNICITY INFORMATION (-6)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory-vista</t>
-  </si>
-  <si>
-    <t>Patient2.raceInformation</t>
-  </si>
-  <si>
-    <t>RACE INFORMATION (-2)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFraceCategory-vista</t>
-  </si>
-  <si>
-    <t>Patient2.maritalStatus</t>
-  </si>
-  <si>
-    <t>MARITAL STATUS (-.05)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus-vista</t>
-  </si>
-  <si>
-    <t>Patient2.religiousPreference</t>
-  </si>
-  <si>
-    <t>RELIGIOUS PREFERENCE (-.08)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1214,7 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
         <v>85</v>
@@ -1314,7 +1314,7 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>87</v>
@@ -1414,7 +1414,7 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>89</v>
@@ -1514,7 +1514,7 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>91</v>
@@ -1614,7 +1614,7 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>93</v>
@@ -1714,7 +1714,7 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>95</v>
@@ -1814,7 +1814,7 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>97</v>
@@ -1914,7 +1914,7 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>99</v>
@@ -2014,7 +2014,7 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>101</v>
@@ -2114,7 +2114,7 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>103</v>
@@ -2214,7 +2214,7 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>105</v>
@@ -2314,7 +2314,7 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>107</v>
@@ -2414,7 +2414,7 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>109</v>
@@ -2514,7 +2514,7 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>111</v>
@@ -2614,7 +2614,7 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>113</v>
@@ -2714,7 +2714,7 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>115</v>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>Patient2.appointment</t>
+    <t>Patient2.integrationControlNumber</t>
   </si>
   <si>
     <t>1</t>
@@ -257,6 +257,173 @@
 </t>
   </si>
   <si>
+    <t>INTEGRATION CONTROL NUMBER (-991.01)</t>
+  </si>
+  <si>
+    <t>Patient2.name</t>
+  </si>
+  <si>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>Patient2.phoneNumberResidence</t>
+  </si>
+  <si>
+    <t>PHONE NUMBER [RESIDENCE] (-.131)</t>
+  </si>
+  <si>
+    <t>Patient2.phoneNumberWork</t>
+  </si>
+  <si>
+    <t>PHONE NUMBER [WORK] (-.132)</t>
+  </si>
+  <si>
+    <t>Patient2.phoneNumberCellular</t>
+  </si>
+  <si>
+    <t>PHONE NUMBER [CELLULAR] (-.134)</t>
+  </si>
+  <si>
+    <t>Patient2.dateOfBirth</t>
+  </si>
+  <si>
+    <t>DATE OF BIRTH (-.03)</t>
+  </si>
+  <si>
+    <t>Patient2.dateOfDeath</t>
+  </si>
+  <si>
+    <t>DATE OF DEATH (-.351)</t>
+  </si>
+  <si>
+    <t>Patient2.streetAddressLine1</t>
+  </si>
+  <si>
+    <t>STREET ADDRESS [LINE 1] (-.111)</t>
+  </si>
+  <si>
+    <t>Patient2.streetAddressLine2</t>
+  </si>
+  <si>
+    <t>STREET ADDRESS [LINE 2] (-.112)</t>
+  </si>
+  <si>
+    <t>Patient2.streetAddressLine3</t>
+  </si>
+  <si>
+    <t>STREET ADDRESS [LINE 3] (-.113)</t>
+  </si>
+  <si>
+    <t>Patient2.city</t>
+  </si>
+  <si>
+    <t>CITY (-.114)</t>
+  </si>
+  <si>
+    <t>Patient2.state</t>
+  </si>
+  <si>
+    <t>STATE (-.115)</t>
+  </si>
+  <si>
+    <t>Patient2.zip4</t>
+  </si>
+  <si>
+    <t>ZIP+4 (-.1112)</t>
+  </si>
+  <si>
+    <t>Patient2.country</t>
+  </si>
+  <si>
+    <t>COUNTRY (-.1173)</t>
+  </si>
+  <si>
+    <t>Patient2.temporaryAddressStartDate</t>
+  </si>
+  <si>
+    <t>TEMPORARY ADDRESS START DATE (-.1217)</t>
+  </si>
+  <si>
+    <t>Patient2.temporaryAddressEndDate</t>
+  </si>
+  <si>
+    <t>TEMPORARY ADDRESS END DATE (-.1218)</t>
+  </si>
+  <si>
+    <t>Patient2.languageDatetime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LanguageDatetime207)
+</t>
+  </si>
+  <si>
+    <t>LANGUAGE DATE/TIME (-7)</t>
+  </si>
+  <si>
+    <t>Patient2.sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>SEX (-.02)</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFadminGender-vista</t>
+  </si>
+  <si>
+    <t>Patient2.selfIdentifiedGender</t>
+  </si>
+  <si>
+    <t>SELF IDENTIFIED GENDER (-.024)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity-vista</t>
+  </si>
+  <si>
+    <t>Patient2.ethnicityInformation</t>
+  </si>
+  <si>
+    <t>ETHNICITY INFORMATION (-6)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory-vista</t>
+  </si>
+  <si>
+    <t>Patient2.raceInformation</t>
+  </si>
+  <si>
+    <t>RACE INFORMATION (-2)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFraceCategory-vista</t>
+  </si>
+  <si>
+    <t>Patient2.maritalStatus</t>
+  </si>
+  <si>
+    <t>MARITAL STATUS (-.05)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus-vista</t>
+  </si>
+  <si>
+    <t>Patient2.religiousPreference</t>
+  </si>
+  <si>
+    <t>RELIGIOUS PREFERENCE (-.08)</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
+  </si>
+  <si>
+    <t>Patient2.appointment</t>
+  </si>
+  <si>
     <t>APPOINTMENT (-1900)</t>
   </si>
   <si>
@@ -268,173 +435,6 @@
   </si>
   <si>
     <t>LABORATORY REFERENCE (-63)</t>
-  </si>
-  <si>
-    <t>Patient2.integrationControlNumber</t>
-  </si>
-  <si>
-    <t>INTEGRATION CONTROL NUMBER (-991.01)</t>
-  </si>
-  <si>
-    <t>Patient2.name</t>
-  </si>
-  <si>
-    <t>NAME (-.01)</t>
-  </si>
-  <si>
-    <t>Patient2.phoneNumberResidence</t>
-  </si>
-  <si>
-    <t>PHONE NUMBER [RESIDENCE] (-.131)</t>
-  </si>
-  <si>
-    <t>Patient2.phoneNumberWork</t>
-  </si>
-  <si>
-    <t>PHONE NUMBER [WORK] (-.132)</t>
-  </si>
-  <si>
-    <t>Patient2.phoneNumberCellular</t>
-  </si>
-  <si>
-    <t>PHONE NUMBER [CELLULAR] (-.134)</t>
-  </si>
-  <si>
-    <t>Patient2.dateOfBirth</t>
-  </si>
-  <si>
-    <t>DATE OF BIRTH (-.03)</t>
-  </si>
-  <si>
-    <t>Patient2.dateOfDeath</t>
-  </si>
-  <si>
-    <t>DATE OF DEATH (-.351)</t>
-  </si>
-  <si>
-    <t>Patient2.streetAddressLine1</t>
-  </si>
-  <si>
-    <t>STREET ADDRESS [LINE 1] (-.111)</t>
-  </si>
-  <si>
-    <t>Patient2.streetAddressLine2</t>
-  </si>
-  <si>
-    <t>STREET ADDRESS [LINE 2] (-.112)</t>
-  </si>
-  <si>
-    <t>Patient2.streetAddressLine3</t>
-  </si>
-  <si>
-    <t>STREET ADDRESS [LINE 3] (-.113)</t>
-  </si>
-  <si>
-    <t>Patient2.city</t>
-  </si>
-  <si>
-    <t>CITY (-.114)</t>
-  </si>
-  <si>
-    <t>Patient2.state</t>
-  </si>
-  <si>
-    <t>STATE (-.115)</t>
-  </si>
-  <si>
-    <t>Patient2.zip4</t>
-  </si>
-  <si>
-    <t>ZIP+4 (-.1112)</t>
-  </si>
-  <si>
-    <t>Patient2.country</t>
-  </si>
-  <si>
-    <t>COUNTRY (-.1173)</t>
-  </si>
-  <si>
-    <t>Patient2.temporaryAddressStartDate</t>
-  </si>
-  <si>
-    <t>TEMPORARY ADDRESS START DATE (-.1217)</t>
-  </si>
-  <si>
-    <t>Patient2.temporaryAddressEndDate</t>
-  </si>
-  <si>
-    <t>TEMPORARY ADDRESS END DATE (-.1218)</t>
-  </si>
-  <si>
-    <t>Patient2.languageDatetime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LanguageDatetime207)
-</t>
-  </si>
-  <si>
-    <t>LANGUAGE DATE/TIME (-7)</t>
-  </si>
-  <si>
-    <t>Patient2.sex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>SEX (-.02)</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFadminGender-vista</t>
-  </si>
-  <si>
-    <t>Patient2.ethnicityInformation</t>
-  </si>
-  <si>
-    <t>ETHNICITY INFORMATION (-6)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory-vista</t>
-  </si>
-  <si>
-    <t>Patient2.raceInformation</t>
-  </si>
-  <si>
-    <t>RACE INFORMATION (-2)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFraceCategory-vista</t>
-  </si>
-  <si>
-    <t>Patient2.maritalStatus</t>
-  </si>
-  <si>
-    <t>MARITAL STATUS (-.05)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus-vista</t>
-  </si>
-  <si>
-    <t>Patient2.religiousPreference</t>
-  </si>
-  <si>
-    <t>RELIGIOUS PREFERENCE (-.08)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
-  </si>
-  <si>
-    <t>Patient2.selfIdentifiedGender</t>
-  </si>
-  <si>
-    <t>SELF IDENTIFIED GENDER (-.024)</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity-vista</t>
   </si>
 </sst>
 </file>
@@ -1114,13 +1114,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1217,10 +1217,10 @@
         <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1271,7 +1271,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1317,10 +1317,10 @@
         <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1371,7 +1371,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1417,10 +1417,10 @@
         <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1471,7 +1471,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1517,10 +1517,10 @@
         <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1571,7 +1571,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1617,10 +1617,10 @@
         <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1671,7 +1671,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1717,10 +1717,10 @@
         <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1771,7 +1771,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1817,10 +1817,10 @@
         <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1871,7 +1871,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1917,10 +1917,10 @@
         <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1971,7 +1971,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2017,10 +2017,10 @@
         <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2071,7 +2071,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2117,10 +2117,10 @@
         <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2171,7 +2171,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2217,10 +2217,10 @@
         <v>79</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2271,7 +2271,7 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>73</v>
@@ -2288,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2317,10 +2317,10 @@
         <v>79</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2371,7 +2371,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2417,10 +2417,10 @@
         <v>79</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2471,7 +2471,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2517,10 +2517,10 @@
         <v>79</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2571,7 +2571,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2614,7 +2614,7 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>113</v>
@@ -2671,7 +2671,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -2714,13 +2714,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2747,13 +2747,11 @@
         <v>72</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>72</v>
@@ -2788,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2814,13 +2812,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2847,13 +2845,11 @@
         <v>72</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>72</v>
@@ -2871,7 +2867,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -2888,10 +2884,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2914,13 +2910,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2947,11 +2943,11 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>72</v>
@@ -2969,7 +2965,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -2986,10 +2982,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3012,13 +3008,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3045,11 +3041,11 @@
         <v>72</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>72</v>
@@ -3067,7 +3063,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3084,10 +3080,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3110,13 +3106,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3143,11 +3139,11 @@
         <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>72</v>
@@ -3165,7 +3161,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3182,10 +3178,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3208,13 +3204,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3241,11 +3237,11 @@
         <v>72</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>72</v>
@@ -3263,7 +3259,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3280,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3306,13 +3302,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3339,11 +3335,13 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>72</v>
@@ -3361,7 +3359,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3404,13 +3402,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3437,11 +3435,13 @@
         <v>72</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>72</v>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -373,7 +373,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFadminGender-vista</t>
+    <t>http://va.gov/fhir/ValueSet/adminGender-vista</t>
   </si>
   <si>
     <t>Patient2.selfIdentifiedGender</t>
@@ -382,7 +382,7 @@
     <t>SELF IDENTIFIED GENDER (-.024)</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFgenderIdentity-vista</t>
+    <t>http://va.gov/fhir/ValueSet/genderIdentity-vista</t>
   </si>
   <si>
     <t>Patient2.ethnicityInformation</t>
@@ -391,7 +391,7 @@
     <t>ETHNICITY INFORMATION (-6)</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFethnicityCategory-vista</t>
+    <t>http://va.gov/fhir/ValueSet/ethnicityCategory-vista</t>
   </si>
   <si>
     <t>Patient2.raceInformation</t>
@@ -400,7 +400,7 @@
     <t>RACE INFORMATION (-2)</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFraceCategory-vista</t>
+    <t>http://va.gov/fhir/ValueSet/raceCategory-vista</t>
   </si>
   <si>
     <t>Patient2.maritalStatus</t>
@@ -409,7 +409,7 @@
     <t>MARITAL STATUS (-.05)</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMaritalStatus-vista</t>
+    <t>http://va.gov/fhir/ValueSet/MaritalStatus-vista</t>
   </si>
   <si>
     <t>Patient2.religiousPreference</t>
@@ -418,7 +418,7 @@
     <t>RELIGIOUS PREFERENCE (-.08)</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFReligion-vista</t>
+    <t>http://va.gov/fhir/ValueSet/Religion-vista</t>
   </si>
   <si>
     <t>Patient2.appointment</t>
@@ -764,7 +764,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.08984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.36328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Patient2.xlsx
+++ b/docs/StructureDefinition-Patient2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
